--- a/dc4_milk_run_routes.xlsx
+++ b/dc4_milk_run_routes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,14 +493,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DPI66437 -&gt; DPI66573 -&gt; DPI66998 -&gt; DPI66386 -&gt; DFT80058 -&gt; DPI64291 -&gt; DPI66104 -&gt; DPI66730 -&gt; DPI66944 -&gt; DPI66591 -&gt; DPI66239 -&gt; DPI70039 -&gt; DPI66945</t>
+          <t>DPI70040 -&gt; DPI64008 -&gt; DPI70035 -&gt; DPI67102 -&gt; DPI66915 -&gt; DPI64506 -&gt; DPI64000 -&gt; DPI64001 -&gt; DPI63902 -&gt; DPI64563 -&gt; DPI65841 -&gt; DPI64137 -&gt; DPI64299</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>13</v>
       </c>
       <c r="E2" t="n">
-        <v>965</v>
+        <v>976</v>
       </c>
       <c r="F2" t="n">
         <v>1613</v>
@@ -509,13 +509,13 @@
         <v>980</v>
       </c>
       <c r="H2" t="n">
-        <v>98.47</v>
+        <v>99.59</v>
       </c>
       <c r="I2" t="n">
-        <v>1152.79</v>
+        <v>1142.94</v>
       </c>
       <c r="J2" t="n">
-        <v>1367149.04</v>
+        <v>1363919.24</v>
       </c>
     </row>
     <row r="3">
@@ -531,14 +531,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DPI67064 -&gt; DPI66619 -&gt; DPI64331 -&gt; DPI65919 -&gt; DPI66377 -&gt; DPI66126 -&gt; DPI64650 -&gt; DPI67217 -&gt; DPI66400 -&gt; DPI64577</t>
+          <t>DPI70149 -&gt; DPI67138 -&gt; DPI67002 -&gt; DPI64644 -&gt; DPI64118 -&gt; DPI63929 -&gt; DPI66395 -&gt; DPI66380 -&gt; DPI66953 -&gt; DPI66759</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>967</v>
+        <v>952</v>
       </c>
       <c r="F3" t="n">
         <v>1613</v>
@@ -547,13 +547,13 @@
         <v>980</v>
       </c>
       <c r="H3" t="n">
-        <v>98.67</v>
+        <v>97.14</v>
       </c>
       <c r="I3" t="n">
-        <v>260.16</v>
+        <v>1252.49</v>
       </c>
       <c r="J3" t="n">
-        <v>1074279.56</v>
+        <v>1399863.25</v>
       </c>
     </row>
     <row r="4">
@@ -569,29 +569,29 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DPI64317 -&gt; DPI64252 -&gt; DPI66640 -&gt; DPI70022 -&gt; DPI67062 -&gt; DPI66532 -&gt; DPI66125 -&gt; DPI64336 -&gt; DPI64237 -&gt; DPI66029 -&gt; DPI64102 -&gt; DPI66497 -&gt; DPI64525 -&gt; DPI64145 -&gt; DPI64079 -&gt; DPI63999</t>
+          <t>DPI64254 -&gt; DPI66995 -&gt; DPI70031 -&gt; DPI66461</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>973</v>
+        <v>498</v>
       </c>
       <c r="F4" t="n">
-        <v>1613</v>
+        <v>1109</v>
       </c>
       <c r="G4" t="n">
-        <v>980</v>
+        <v>660</v>
       </c>
       <c r="H4" t="n">
-        <v>99.29000000000001</v>
+        <v>75.45</v>
       </c>
       <c r="I4" t="n">
-        <v>1038.34</v>
+        <v>142.15</v>
       </c>
       <c r="J4" t="n">
-        <v>1329599.68</v>
+        <v>901483.97</v>
       </c>
     </row>
     <row r="5">
@@ -607,14 +607,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DPI66501 -&gt; DPI66280 -&gt; DPI66926 -&gt; DPI66031 -&gt; DPI64408 -&gt; DPI66333 -&gt; DPI64227 -&gt; DPI64470</t>
+          <t>DPI66594 -&gt; DPI64091 -&gt; DPI70090 -&gt; DPI64239 -&gt; DPI64045 -&gt; DPI66503 -&gt; DPI64024 -&gt; DPI67047 -&gt; DPI64191</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>953</v>
+        <v>973</v>
       </c>
       <c r="F5" t="n">
         <v>1613</v>
@@ -623,13 +623,13 @@
         <v>980</v>
       </c>
       <c r="H5" t="n">
-        <v>97.23999999999999</v>
+        <v>99.29000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>287.77</v>
+        <v>407.08</v>
       </c>
       <c r="J5" t="n">
-        <v>1083336.44</v>
+        <v>1122482.18</v>
       </c>
     </row>
     <row r="6">
@@ -645,14 +645,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DPI67093 -&gt; DPI64720 -&gt; DPI64741 -&gt; DPI64203 -&gt; DPI66119 -&gt; DPI67050 -&gt; DPI70058 -&gt; DPI64310 -&gt; DPI64279 -&gt; DPI64043 -&gt; DPI70256 -&gt; DPI66929</t>
+          <t>DPI63904 -&gt; DPI66091 -&gt; DPI64374 -&gt; DPI70166 -&gt; DPI70095 -&gt; DPI66938 -&gt; DPI64108</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>980</v>
+        <v>863</v>
       </c>
       <c r="F6" t="n">
         <v>1613</v>
@@ -661,13 +661,13 @@
         <v>980</v>
       </c>
       <c r="H6" t="n">
-        <v>100</v>
+        <v>88.06</v>
       </c>
       <c r="I6" t="n">
-        <v>896.37</v>
+        <v>656.1900000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>1283018.27</v>
+        <v>1204216.51</v>
       </c>
     </row>
     <row r="7">
@@ -683,14 +683,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DPI66094 -&gt; DPI70320 -&gt; DPI70148 -&gt; DPI64207 -&gt; DPI64469 -&gt; DPI64706 -&gt; DPI64106 -&gt; DPI64083 -&gt; DPI66548 -&gt; DPI64073 -&gt; DPI70069 -&gt; DFT80095</t>
+          <t>DPI70165 -&gt; DPI67004 -&gt; DPI64175 -&gt; DPI66100 -&gt; DPI66491 -&gt; DPI70234 -&gt; DPI64085 -&gt; DPI66060 -&gt; DPI64619 -&gt; DPI66555</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>978</v>
+        <v>915</v>
       </c>
       <c r="F7" t="n">
         <v>1613</v>
@@ -699,13 +699,13 @@
         <v>980</v>
       </c>
       <c r="H7" t="n">
-        <v>99.8</v>
+        <v>93.37</v>
       </c>
       <c r="I7" t="n">
-        <v>1087.06</v>
+        <v>470.82</v>
       </c>
       <c r="J7" t="n">
-        <v>1345585.37</v>
+        <v>1143396.75</v>
       </c>
     </row>
     <row r="8">
@@ -721,14 +721,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DPI65998 -&gt; DPI64140 -&gt; DPI67181 -&gt; DPI70306 -&gt; DPI63978 -&gt; DPI64752 -&gt; DPI66733 -&gt; DPI67014 -&gt; DPI65969</t>
+          <t>DPI64281 -&gt; DPI64561 -&gt; DPI65827 -&gt; DPI66974 -&gt; DPI66511 -&gt; DPI66512 -&gt; DPI66265 -&gt; DPI70254 -&gt; DPI67214 -&gt; DPI70327</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="F8" t="n">
         <v>1613</v>
@@ -737,13 +737,13 @@
         <v>980</v>
       </c>
       <c r="H8" t="n">
-        <v>97.34999999999999</v>
+        <v>97.23999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>297.73</v>
+        <v>281.3</v>
       </c>
       <c r="J8" t="n">
-        <v>1086606.06</v>
+        <v>1081215.26</v>
       </c>
     </row>
     <row r="9">
@@ -759,14 +759,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DPI66410 -&gt; DPI65877 -&gt; DPI64240 -&gt; DPI66970 -&gt; DPI66622 -&gt; DPI70261 -&gt; DPI67021 -&gt; DPI66621 -&gt; DPI64377</t>
+          <t>DPI66669 -&gt; DPI64400 -&gt; DPI70228 -&gt; DPI64513 -&gt; DPI64364 -&gt; DPI65967 -&gt; DPI65825 -&gt; DPI64694</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>961</v>
+        <v>867</v>
       </c>
       <c r="F9" t="n">
         <v>1613</v>
@@ -775,13 +775,13 @@
         <v>980</v>
       </c>
       <c r="H9" t="n">
-        <v>98.06</v>
+        <v>88.47</v>
       </c>
       <c r="I9" t="n">
-        <v>288</v>
+        <v>378.06</v>
       </c>
       <c r="J9" t="n">
-        <v>1083413.88</v>
+        <v>1112962.75</v>
       </c>
     </row>
     <row r="10">
@@ -797,14 +797,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>DPI63823 -&gt; DPI70091 -&gt; DPI65840 -&gt; DPI65915 -&gt; DPI66538 -&gt; DPI67183 -&gt; DPI64602 -&gt; DPI65779 -&gt; DPI64019 -&gt; DPI66194 -&gt; DPI67110</t>
+          <t>DPI70221 -&gt; DPI70082 -&gt; DPI64711 -&gt; DPI67245 -&gt; DPI65824 -&gt; DPI65981 -&gt; DPI65927 -&gt; DPI67043 -&gt; DPI64606 -&gt; DPI64462</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="F10" t="n">
         <v>1613</v>
@@ -813,13 +813,13 @@
         <v>980</v>
       </c>
       <c r="H10" t="n">
-        <v>99.90000000000001</v>
+        <v>99.8</v>
       </c>
       <c r="I10" t="n">
-        <v>274.01</v>
+        <v>288.05</v>
       </c>
       <c r="J10" t="n">
-        <v>1078824.02</v>
+        <v>1083429.72</v>
       </c>
     </row>
     <row r="11">
@@ -835,14 +835,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>DPI67179 -&gt; DPI66076 -&gt; DPI66660 -&gt; DPI66521 -&gt; DPI66136 -&gt; DPI63951 -&gt; DPI65789 -&gt; DPI64631 -&gt; DPI70140</t>
+          <t>DPI66372 -&gt; DPI64247 -&gt; DPI64361 -&gt; DPI65875 -&gt; DPI66329 -&gt; DPI66127 -&gt; DPI66748 -&gt; DPI64253 -&gt; DPI63898 -&gt; DPI64543 -&gt; DPI64590</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
-        <v>963</v>
+        <v>954</v>
       </c>
       <c r="F11" t="n">
         <v>1613</v>
@@ -851,165 +851,13 @@
         <v>980</v>
       </c>
       <c r="H11" t="n">
-        <v>98.27</v>
+        <v>97.34999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>265.18</v>
+        <v>592.11</v>
       </c>
       <c r="J11" t="n">
-        <v>1075924.61</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>R11</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>DC_4</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>DPI70176 -&gt; DPI66755 -&gt; DPI64026 -&gt; DPI66389 -&gt; DPI65993 -&gt; DPI67126 -&gt; DPI67118 -&gt; DPI64250 -&gt; DPI66422 -&gt; DPI64520</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>10</v>
-      </c>
-      <c r="E12" t="n">
-        <v>972</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1613</v>
-      </c>
-      <c r="G12" t="n">
-        <v>980</v>
-      </c>
-      <c r="H12" t="n">
-        <v>99.18000000000001</v>
-      </c>
-      <c r="I12" t="n">
-        <v>273.71</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1078724.15</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>R12</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>DC_4</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>DPI64600 -&gt; DPI70216 -&gt; DPI64428 -&gt; DPI66940 -&gt; DPI63945 -&gt; DPI64350 -&gt; DPI66729 -&gt; DPI66122 -&gt; DPI64418 -&gt; DPI66326 -&gt; DPI64246 -&gt; DPI63936 -&gt; DPI64703 -&gt; DPI66652 -&gt; DPI64641</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>15</v>
-      </c>
-      <c r="E13" t="n">
-        <v>977</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1613</v>
-      </c>
-      <c r="G13" t="n">
-        <v>980</v>
-      </c>
-      <c r="H13" t="n">
-        <v>99.69</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1153.68</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1367444.02</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>R13</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>DC_4</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>DPI66241 -&gt; DPI66191 -&gt; DPI66359 -&gt; DPI66014 -&gt; DPI63950 -&gt; DPI66042 -&gt; DPI70104 -&gt; DPI66688 -&gt; DPI66522 -&gt; DPI63813</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10</v>
-      </c>
-      <c r="E14" t="n">
-        <v>980</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1613</v>
-      </c>
-      <c r="G14" t="n">
-        <v>980</v>
-      </c>
-      <c r="H14" t="n">
-        <v>100</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1077.19</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1342345.96</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>R14</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>DC_4</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>DPI66224 -&gt; DPI66999 -&gt; DPI70032 -&gt; DPI66626 -&gt; DPI66578 -&gt; DPI67042 -&gt; DPI70057 -&gt; DPI66378 -&gt; DPI66053 -&gt; DPI66685</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>10</v>
-      </c>
-      <c r="E15" t="n">
-        <v>975</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1613</v>
-      </c>
-      <c r="G15" t="n">
-        <v>980</v>
-      </c>
-      <c r="H15" t="n">
-        <v>99.48999999999999</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1103.42</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1350951.3</v>
+        <v>1183192.14</v>
       </c>
     </row>
   </sheetData>

--- a/dc4_milk_run_routes.xlsx
+++ b/dc4_milk_run_routes.xlsx
@@ -515,7 +515,7 @@
         <v>1142.94</v>
       </c>
       <c r="J2" t="n">
-        <v>1363919.24</v>
+        <v>473891.24</v>
       </c>
     </row>
     <row r="3">
@@ -553,7 +553,7 @@
         <v>1252.49</v>
       </c>
       <c r="J3" t="n">
-        <v>1399863.25</v>
+        <v>509835.25</v>
       </c>
     </row>
     <row r="4">
@@ -591,7 +591,7 @@
         <v>142.15</v>
       </c>
       <c r="J4" t="n">
-        <v>901483.97</v>
+        <v>126583.97</v>
       </c>
     </row>
     <row r="5">
@@ -629,7 +629,7 @@
         <v>407.08</v>
       </c>
       <c r="J5" t="n">
-        <v>1122482.18</v>
+        <v>232454.18</v>
       </c>
     </row>
     <row r="6">
@@ -667,7 +667,7 @@
         <v>656.1900000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>1204216.51</v>
+        <v>314188.51</v>
       </c>
     </row>
     <row r="7">
@@ -705,7 +705,7 @@
         <v>470.82</v>
       </c>
       <c r="J7" t="n">
-        <v>1143396.75</v>
+        <v>253368.75</v>
       </c>
     </row>
     <row r="8">
@@ -743,7 +743,7 @@
         <v>281.3</v>
       </c>
       <c r="J8" t="n">
-        <v>1081215.26</v>
+        <v>191187.26</v>
       </c>
     </row>
     <row r="9">
@@ -781,7 +781,7 @@
         <v>378.06</v>
       </c>
       <c r="J9" t="n">
-        <v>1112962.75</v>
+        <v>222934.75</v>
       </c>
     </row>
     <row r="10">
@@ -819,7 +819,7 @@
         <v>288.05</v>
       </c>
       <c r="J10" t="n">
-        <v>1083429.72</v>
+        <v>193401.72</v>
       </c>
     </row>
     <row r="11">
@@ -857,7 +857,7 @@
         <v>592.11</v>
       </c>
       <c r="J11" t="n">
-        <v>1183192.14</v>
+        <v>293164.14</v>
       </c>
     </row>
   </sheetData>
